--- a/docs/xlsx/jobs-2026-09-07.xlsx
+++ b/docs/xlsx/jobs-2026-09-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="240">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,543 @@
     <t>Link</t>
   </si>
   <si>
+    <t>2027 Forestry Summer Internship - Milford ME</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Milford, ME</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$16 - $18 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---milford-me-milford-maine/4445705038</t>
+  </si>
+  <si>
+    <t>Assistant Director of Policy and Budget: Minnesota Department of Natural Resources: Division of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$108,346 - $155,159 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-director-of-policy-and-budget-minnesota-department-of-natural-resources-division-of-fish-and-wildlife-st-paul-minnesota/1705299314</t>
+  </si>
+  <si>
+    <t>Assistant Environmental Permitting Supervisor: Wetland Specialist (EP4) - Permanent - 2026-07307</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$6,384 - $8,583 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-environmental-permitting-supervisor-wetland-specialist-ep4---permanent---2026-07307-olympia-washington/3464195066</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Biology</t>
+  </si>
+  <si>
+    <t>Stetson University</t>
+  </si>
+  <si>
+    <t>DeLand, FL</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-of-biology-deland-florida/6323617312</t>
+  </si>
+  <si>
+    <t>Climate Finance Specialist</t>
+  </si>
+  <si>
+    <t>National Caucus of Environmental Legislators</t>
+  </si>
+  <si>
+    <t>Washington, Remote</t>
+  </si>
+  <si>
+    <t>$74,000 - $83,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grid-specialist---climate--energy-washington-remote/8094815586</t>
+  </si>
+  <si>
+    <t>Commercial Fisheries and Seafood Extension Specialist</t>
+  </si>
+  <si>
+    <t>Texas Sea Grant</t>
+  </si>
+  <si>
+    <t>Galveston, TX</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-commercial-fisheries-and-seafood-extension-specialist-galveston-texas/5709498472</t>
+  </si>
+  <si>
+    <t>Communications &amp; Development Specialist</t>
+  </si>
+  <si>
+    <t>Grand Traverse Conservation District &amp; Boardman River Nature Center</t>
+  </si>
+  <si>
+    <t>Traverse City, MI</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications--development-specialist-traverse-city-michigan/3950130849</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Savanna Institute</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$62,000 - $68,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development--communications-manager-remote-remote/6477945928</t>
+  </si>
+  <si>
+    <t>Director of Lands</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>Chester, NJ</t>
+  </si>
+  <si>
+    <t>$114,000 - $127,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-lands-chester-new-jersey/9098701621</t>
+  </si>
+  <si>
+    <t>Educator/ Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Hidden Villa</t>
+  </si>
+  <si>
+    <t>Los Altos, CA</t>
+  </si>
+  <si>
+    <t>$28.50 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-educator-volunteer-coordinator-los-altos-california/9540670216</t>
+  </si>
+  <si>
+    <t>Emerging Leaders Program Summer Associates</t>
+  </si>
+  <si>
+    <t>Washington Trails Association (WTA)</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-emerging-leaders-program-summer-associates-seattle-washington/9904267310</t>
+  </si>
+  <si>
+    <t>Fish Hatchery Specialist 3 - Naselle River Hatchery - Permanent - 2026-07274</t>
+  </si>
+  <si>
+    <t>Naselle, WA</t>
+  </si>
+  <si>
+    <t>$4,633 - $6,229 per month</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hatchery-specialist-3---naselle-river-hatchery---permanent---2026-07274-naselle-washington/7776067292</t>
+  </si>
+  <si>
+    <t>Fleet Manager</t>
+  </si>
+  <si>
+    <t>American Prairie</t>
+  </si>
+  <si>
+    <t>Lewistown, MT</t>
+  </si>
+  <si>
+    <t>$26.50 - $34.50 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fleet-manager-lewistown-montana/4865494198</t>
+  </si>
+  <si>
+    <t>GIS Consultant and Community Educator (Limited Term Contract)</t>
+  </si>
+  <si>
+    <t>CHEM Allyance</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$40 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gis-consultant-and-community-educator-limited-term-contract-portland-oregon/7287700975</t>
+  </si>
+  <si>
+    <t>Green Corps Campaigner</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>New Orleans, LA</t>
+  </si>
+  <si>
+    <t>Pay and benefits are prorated for the length of your campaign position. The target annual compensation for this position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location and start date).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-new-orleans-louisiana/2206528277</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-philadelphia-pennsylvania/6632770349</t>
+  </si>
+  <si>
+    <t>Charlotte, NC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-charlotte-north-carolina/3515509602</t>
+  </si>
+  <si>
+    <t>Miami, FL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-miami-florida/5551049033</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-charleston-south-carolina/9175420853</t>
+  </si>
+  <si>
+    <t>Nashville, TN</t>
+  </si>
+  <si>
+    <t>Pay and benefits are prorated for the length of your campaign position, The target annual compensation for this position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location and start date).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-nashville-tennessee/8477936848</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-phoenix-arizona/3235368514</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-denver-colorado/5340449074</t>
+  </si>
+  <si>
+    <t>Grid Specialist - Climate &amp; Energy</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grid-specialist---climate--energy-washington-remote/7341453620</t>
+  </si>
+  <si>
+    <t>Hubbard Conservation Fellow</t>
+  </si>
+  <si>
+    <t>Wood River, KS</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$17.85 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hubbard-conservation-fellow-wood-river-kansas/5307789502</t>
+  </si>
+  <si>
+    <t>Natural Resources Front Desk Office Assistant</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Castle Rock, WA</t>
+  </si>
+  <si>
+    <t>$3,485 - $4,633 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-front-desk-office-assistant-castle-rock-washington/6548506909</t>
+  </si>
+  <si>
+    <t>NPS / Historical Preservation Training Center - Southeast Regional Support Team</t>
+  </si>
+  <si>
+    <t>Conservation Legacy</t>
+  </si>
+  <si>
+    <t>Jacksonville, FL</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nps--historical-preservation-training-center---southeast-regional-support-team-jacksonville-florida/6148746165</t>
+  </si>
+  <si>
+    <t>Onsite Resource Specialist (Natural Resource Specialist 3 – Environmental Health Specialist / Natural Resource Specialist 3 – Underfill)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Environmental Quality</t>
+  </si>
+  <si>
+    <t>Medford, OR</t>
+  </si>
+  <si>
+    <t>$5,712 - $8,757 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-onsite-resource-specialist-natural-resource-specialist-3--environmental-health-specialist--natural-resource-specialist-3--underfill-medford-oregon/8352559679</t>
+  </si>
+  <si>
+    <t>Product Sales Contracts Specialist</t>
+  </si>
+  <si>
+    <t>Enumclaw, WA</t>
+  </si>
+  <si>
+    <t>$54,180 - $72,804 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-product-sales-contracts-specialist-enumclaw-washington/1033877305</t>
+  </si>
+  <si>
+    <t>Re5 Coral Restoration Internship</t>
+  </si>
+  <si>
+    <t>Reef Renewal USA</t>
+  </si>
+  <si>
+    <t>Tavernier, FL</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>marine-biology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-re5-coral-restoration-internship-tavernier-florida/3660767571</t>
+  </si>
+  <si>
+    <t>RT-QulC Laboratory Research Technician</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$33 per hour</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rt-qulc-laboratory-research-technician-cheyenne-wyoming/5233459622</t>
+  </si>
+  <si>
+    <t>Sanctuary Wildlife Keeper Intern</t>
+  </si>
+  <si>
+    <t>KSTR Wildlife Rescue</t>
+  </si>
+  <si>
+    <t>Quepos, Latin America</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Unpaid position</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sanctuary-wildlife-keeper-intern-quepos-latin-america/4012391800</t>
+  </si>
+  <si>
+    <t>Senior Environmental Specialist</t>
+  </si>
+  <si>
+    <t>ABR, Inc.</t>
+  </si>
+  <si>
+    <t>Fairbanks, Remote</t>
+  </si>
+  <si>
+    <t>$55+ per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-environmental-specialist-fairbanks-remote/5438813651</t>
+  </si>
+  <si>
+    <t>Senior Fish Health Microbiologist - Microbiologist 4 - Permanent - 2026-07261</t>
+  </si>
+  <si>
+    <t>$6,870 - $9,246 per month</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-fish-health-microbiologist---microbiologist-4---permanent---2026-07261-olympia-washington/5065902134</t>
+  </si>
+  <si>
+    <t>Sr. Planner - Urban Forestry Officer</t>
+  </si>
+  <si>
+    <t>City of Fort Worth</t>
+  </si>
+  <si>
+    <t>Fort Worth, TX</t>
+  </si>
+  <si>
+    <t>$71,661 - $93,159 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sr-planner---urban-forestry-officer-fort-worth-texas/2618143943</t>
+  </si>
+  <si>
+    <t>Urban Forest Stewardship Specialist (Botanic Specialist II - Forestry)</t>
+  </si>
+  <si>
+    <t>City of Portland</t>
+  </si>
+  <si>
+    <t>$81,556.80 - $104,062.40 per year</t>
+  </si>
+  <si>
+    <t>botany-forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-urban-forest-stewardship-specialist-botanic-specialist-ii---forestry-portland-oregon/1273934981</t>
+  </si>
+  <si>
+    <t>USDA-ARS Postdoctoral Research Fellowship in Soil Science</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Pendleton, OR</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>The yearly stipend is $73,932. A relocation award will be provided as well as a health insurance stipend supplement.</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-postdoctoral-research-fellowship-in-soil-science-pendleton-oregon/3943609489</t>
+  </si>
+  <si>
     <t>AI Governance Roles, European Team - Based in Europe</t>
   </si>
   <si>
@@ -77,6 +614,126 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/2e35ef7f75de4bfba0f96effc1c7d621-community-organizer-street-vendor-project-urban-justice-center-new-york</t>
+  </si>
+  <si>
+    <t>Farmworker Association of Florida, Inc.</t>
+  </si>
+  <si>
+    <t>Apopka, Florida</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30d34241e68940b1aac0ce089d9bc2d6-community-organizer-farmworker-association-of-florida-inc-apopka</t>
+  </si>
+  <si>
+    <t>Expert season Fundraiser</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Remote (IE)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5615d1a8b4b490f852aecd2dc5d3467-expert-season-fundraiser-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Founding Conversation &amp; Content Builder</t>
+  </si>
+  <si>
+    <t>Nextus</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Community Development, Community Development, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10ea82e9a762487cad7a2b02ae3c3d9c-founding-conversation-content-builder-nextus-torornto</t>
+  </si>
+  <si>
+    <t>Medical Director in Belize - Live Abroad</t>
+  </si>
+  <si>
+    <t>Hillside Health Care</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Belize, BZ</t>
+  </si>
+  <si>
+    <t>USD 18804.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9ae100c89434ee2a55793f176d19271-medical-director-in-belize-live-abroad-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Public Health Director in beautiful Belize</t>
+  </si>
+  <si>
+    <t>Punta Gorda, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb3df16d12b44a258faf611f683cef7e-public-health-director-in-beautiful-belize-hillside-health-care-punta-gorda</t>
+  </si>
+  <si>
+    <t>Speech-Language Pathologist Volunteer</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18804.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/858bd55c47964be099cb053f6c80cbdb-speech-language-pathologist-volunteer-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Syringe Exchange Supply Hub Program Coordinator</t>
+  </si>
+  <si>
+    <t>Perfectly Flawed Foundation</t>
+  </si>
+  <si>
+    <t>La Salle, Illinois</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4613062b86b7463e94c391f171d0cc7a-syringe-exchange-supply-hub-program-coordinator-perfectly-flawed-foundation-la-salle</t>
   </si>
 </sst>
 </file>
@@ -462,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -501,8 +1158,874 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" t="s">
+        <v>158</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -558,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -599,48 +2122,209 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -648,6 +2332,13 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-07.xlsx
+++ b/docs/xlsx/jobs-2026-09-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="312">
   <si>
     <t>Title</t>
   </si>
@@ -598,15 +598,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/7e5bdb1226a3409d9b6871ff110d113d-ai-governance-roles-european-team-based-in-europe-the-future-society-brussels</t>
   </si>
   <si>
+    <t>APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
+  </si>
+  <si>
+    <t>Centros Barriales - Municipalidad de Vicente López</t>
+  </si>
+  <si>
+    <t>Florida, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b6fa5f49e9d24051a5efc3cc2f7cfbb5-apoyo-escolar-centro-barrial-la-lucila-centros-barriales-municipalidad-de-vicente-lopez-florida</t>
+  </si>
+  <si>
+    <t>Associate Director, Development (Corporate Partnerships)</t>
+  </si>
+  <si>
+    <t>Heritage of Pride, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8de44a926b54f25870dd257cea91f47-associate-director-development-corporate-partnerships-heritage-of-pride-inc-new-york</t>
+  </si>
+  <si>
     <t>Community Organizer</t>
   </si>
   <si>
     <t>Street Vendor Project - Urban Justice Center</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 58140.00 - 71110.19/year</t>
   </si>
   <si>
@@ -631,6 +664,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/30d34241e68940b1aac0ce089d9bc2d6-community-organizer-farmworker-association-of-florida-inc-apopka</t>
   </si>
   <si>
+    <t>Director of Communications and Development</t>
+  </si>
+  <si>
+    <t>Iniciativa de los Derechos de la Mujer</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/739b14d705044a9b8bc5bcb2c4224be1-director-of-communications-and-development-iniciativa-de-los-derechos-de-la-mujer-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Antigua Guatemala, Sacatepéquez, GT</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/495d1015474144ffaecd72c2bc466a48-director-of-communications-and-development-iniciativa-de-los-derechos-de-la-mujer-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Ejecutivo Telefónico</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles y Juveniles SOS de México, I. A. P</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 9000.00 - 10000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e4fed33d4384f9c8bd0e86a15d50c41-ejecutivo-telefonico-aldeas-infantiles-y-juveniles-sos-de-mexico-i-a-p-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Event Manager, PrideFest (NYC Pride)</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dbe07deb4a6d40a4a33e8af6d9489d5b-event-manager-pridefest-nyc-pride-heritage-of-pride-inc-new-york</t>
+  </si>
+  <si>
+    <t>Event Manager: The March (NYC Pride)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20a7d155fce5407197f96b60d118030a-event-manager-the-march-nyc-pride-heritage-of-pride-inc-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>USD 66500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec39f6fbb0ee4a6e8f760824666c388d-executive-assistant-heritage-of-pride-inc-new-york</t>
+  </si>
+  <si>
     <t>Expert season Fundraiser</t>
   </si>
   <si>
@@ -661,15 +757,60 @@
     <t>Part Time</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Community Development, Community Development, International Relations</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/10ea82e9a762487cad7a2b02ae3c3d9c-founding-conversation-content-builder-nextus-torornto</t>
   </si>
   <si>
+    <t>Head of Finance</t>
+  </si>
+  <si>
+    <t>CIVICUS</t>
+  </si>
+  <si>
+    <t>USD 87845.85 - 87845.85/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/540f0115163e45ed8e81deefd24dd85e-head-of-finance-civicus-johannesburg</t>
+  </si>
+  <si>
+    <t>Health and Justice Reform Policy Associate</t>
+  </si>
+  <si>
+    <t>Legal Action Center (NYC, D.C.)</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98c7b11b497c4c18aba0e57a7cd7dd83-health-and-justice-reform-policy-associate-legal-action-center-nyc-dc-washington</t>
+  </si>
+  <si>
+    <t>Literacy Hub Lead</t>
+  </si>
+  <si>
+    <t>Start Lighthouse</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90c0381cf7a34b68974b5f2e7c9f4750-literacy-hub-lead-start-lighthouse-bronx-county</t>
+  </si>
+  <si>
     <t>Medical Director in Belize - Live Abroad</t>
   </si>
   <si>
@@ -688,6 +829,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/f9ae100c89434ee2a55793f176d19271-medical-director-in-belize-live-abroad-hillside-health-care-eldridgeville</t>
   </si>
   <si>
+    <t>Médico/a de Aldea</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 18000.00 - 19000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5a3f060d50f4bb99d1126808e1ebc48-medicoa-de-aldea-aldeas-infantiles-y-juveniles-sos-de-mexico-i-a-p-tuxtla-gutierrez</t>
+  </si>
+  <si>
     <t>Public Health Director in beautiful Belize</t>
   </si>
   <si>
@@ -703,6 +856,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/fb3df16d12b44a258faf611f683cef7e-public-health-director-in-beautiful-belize-hillside-health-care-punta-gorda</t>
   </si>
   <si>
+    <t>Senior Administrative Associate</t>
+  </si>
+  <si>
+    <t>The Jack, Joseph and Morton Mandel Foundation</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5eb37af651f4ceda6fdc24a0cc2809d-senior-administrative-associate-the-jack-joseph-and-morton-mandel-foundation-brookline</t>
+  </si>
+  <si>
     <t>Speech-Language Pathologist Volunteer</t>
   </si>
   <si>
@@ -718,6 +889,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/858bd55c47964be099cb053f6c80cbdb-speech-language-pathologist-volunteer-hillside-health-care-eldridgeville</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>National Congress of the Federated States of Micronesia</t>
+  </si>
+  <si>
+    <t>Palikir, Pohnpei, FM</t>
+  </si>
+  <si>
+    <t>USD 61235.00 - 68138.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Legal Assistance, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/ab78201b3a114394a4cd6d7646d61d3f-staff-attorney-national-congress-of-the-federated-states-of-micronesia-palikir</t>
+  </si>
+  <si>
+    <t>Staff Attorney- San Joaquin Valley</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>Remote (Fresno, California)</t>
+  </si>
+  <si>
+    <t>USD 93509.70/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/761896e5faaf42a389a5f2c2ff74bd21-staff-attorney-san-joaquin-valley-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
     <t>Syringe Exchange Supply Hub Program Coordinator</t>
   </si>
   <si>
@@ -734,6 +941,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4613062b86b7463e94c391f171d0cc7a-syringe-exchange-supply-hub-program-coordinator-perfectly-flawed-foundation-la-salle</t>
+  </si>
+  <si>
+    <t>Volunteer Manager (NYC Pride)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/475a639354cb4276909d8fff0e50ea9c-volunteer-manager-nyc-pride-heritage-of-pride-inc-new-york</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2168,163 +2384,531 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
         <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" t="s">
         <v>208</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>209</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" t="s">
         <v>212</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" t="s">
         <v>213</v>
       </c>
-      <c r="C6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>214</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="F6" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
         <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D8" t="s">
         <v>190</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
         <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F9" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
         <v>190</v>
       </c>
       <c r="E10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" t="s">
+        <v>204</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>237</v>
       </c>
-      <c r="F10" t="s">
+      <c r="B13" t="s">
         <v>238</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="C13" t="s">
         <v>239</v>
+      </c>
+      <c r="D13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" t="s">
+        <v>242</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F15" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D16" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>259</v>
+      </c>
+      <c r="B17" t="s">
+        <v>260</v>
+      </c>
+      <c r="C17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" t="s">
+        <v>263</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" t="s">
+        <v>268</v>
+      </c>
+      <c r="F18" t="s">
+        <v>269</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" t="s">
+        <v>226</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>275</v>
+      </c>
+      <c r="B20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>280</v>
+      </c>
+      <c r="B21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" t="s">
+        <v>283</v>
+      </c>
+      <c r="F21" t="s">
+        <v>284</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
+        <v>287</v>
+      </c>
+      <c r="D22" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" t="s">
+        <v>288</v>
+      </c>
+      <c r="F22" t="s">
+        <v>289</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+      <c r="B23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>294</v>
+      </c>
+      <c r="F23" t="s">
+        <v>295</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>297</v>
+      </c>
+      <c r="B24" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" t="s">
+        <v>300</v>
+      </c>
+      <c r="F24" t="s">
+        <v>301</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B25" t="s">
+        <v>304</v>
+      </c>
+      <c r="C25" t="s">
+        <v>305</v>
+      </c>
+      <c r="D25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" t="s">
+        <v>306</v>
+      </c>
+      <c r="F25" t="s">
+        <v>307</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" t="s">
+        <v>202</v>
+      </c>
+      <c r="D26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" t="s">
+        <v>310</v>
+      </c>
+      <c r="F26" t="s">
+        <v>204</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -2339,6 +2923,22 @@
     <hyperlink ref="H8" r:id="rId7"/>
     <hyperlink ref="H9" r:id="rId8"/>
     <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-07.xlsx
+++ b/docs/xlsx/jobs-2026-09-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="314">
   <si>
     <t>Title</t>
   </si>
@@ -725,6 +725,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ec39f6fbb0ee4a6e8f760824666c388d-executive-assistant-heritage-of-pride-inc-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant (NYC Pride)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec39f6fbb0ee4a6e8f760824666c388d-executive-assistant-nyc-pride-heritage-of-pride-inc-new-york</t>
   </si>
   <si>
     <t>Expert season Fundraiser</t>
@@ -2297,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2594,321 +2600,344 @@
         <v>237</v>
       </c>
       <c r="B13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="C13" t="s">
-        <v>239</v>
-      </c>
-      <c r="D13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F13" t="s">
-        <v>242</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F14" t="s">
         <v>244</v>
       </c>
-      <c r="B14" t="s">
+      <c r="H14" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="C14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
         <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="E15" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="F15" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
         <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F16" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D17" t="s">
         <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D18" t="s">
         <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D19" t="s">
         <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F19" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B20" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D20" t="s">
         <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D21" t="s">
         <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B22" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D22" t="s">
         <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F22" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B23" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="C23" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D23" t="s">
         <v>190</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D24" t="s">
         <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D25" t="s">
         <v>190</v>
       </c>
       <c r="E25" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F25" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="D26" t="s">
         <v>190</v>
       </c>
       <c r="E26" t="s">
+        <v>308</v>
+      </c>
+      <c r="F26" t="s">
+        <v>309</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F26" t="s">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" t="s">
+        <v>202</v>
+      </c>
+      <c r="D27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" t="s">
+        <v>312</v>
+      </c>
+      <c r="F27" t="s">
         <v>204</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>311</v>
+      <c r="H27" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -2939,6 +2968,7 @@
     <hyperlink ref="H24" r:id="rId23"/>
     <hyperlink ref="H25" r:id="rId24"/>
     <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
